--- a/data/trans_dic/Predimed_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,77; 86,74</t>
+          <t>80,18; 86,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,99; 85,86</t>
+          <t>80,97; 86,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,42; 85,59</t>
+          <t>81,55; 85,58</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,37; 90,1</t>
+          <t>83,26; 90,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,09; 86,4</t>
+          <t>78,21; 86,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,51; 87,21</t>
+          <t>81,52; 87,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,73; 81,59</t>
+          <t>73,92; 81,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,13; 80,65</t>
+          <t>74,79; 80,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,4; 80,21</t>
+          <t>75,51; 79,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,07; 87,74</t>
+          <t>82,05; 87,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,03; 84,78</t>
+          <t>78,99; 84,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,11; 85,26</t>
+          <t>81,07; 85,23</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>376344; 404168</t>
+          <t>373587; 402065</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>566542; 600581</t>
+          <t>566360; 601966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>948893; 997551</t>
+          <t>950418; 997429</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1778602; 1922254</t>
+          <t>1776272; 1939206</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1658936; 1835271</t>
+          <t>1661291; 1832165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3470465; 3712908</t>
+          <t>3470960; 3715138</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>456737; 505376</t>
+          <t>457917; 503817</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>474250; 509092</t>
+          <t>472054; 508704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>942935; 1003208</t>
+          <t>944379; 999954</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2641630; 2823998</t>
+          <t>2640904; 2813367</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2730348; 2929184</t>
+          <t>2729210; 2933743</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5413312; 5690199</t>
+          <t>5410152; 5688034</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,18; 86,29</t>
+          <t>80,14; 86,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 86,06</t>
+          <t>81,9; 86,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,55; 85,58</t>
+          <t>82,02; 85,64</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,26; 90,9</t>
+          <t>81,89; 85,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,21; 86,25</t>
+          <t>79,6; 82,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,52; 87,26</t>
+          <t>81,18; 83,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,92; 81,33</t>
+          <t>73,25; 80,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,79; 80,59</t>
+          <t>74,71; 80,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,51; 79,95</t>
+          <t>74,92; 79,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,41</t>
+          <t>80,87; 83,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,99; 84,91</t>
+          <t>79,74; 82,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,07; 85,23</t>
+          <t>80,77; 82,6</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>390715</t>
+          <t>432072</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>585111</t>
+          <t>642015</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>1074087</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>373587; 402065</t>
+          <t>414149; 447026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>566360; 601966</t>
+          <t>624657; 656358</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>950418; 997429</t>
+          <t>1049375; 1095700</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1831429</t>
+          <t>1733489</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1745680</t>
+          <t>1655562</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3577110</t>
+          <t>3389050</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1776272; 1939206</t>
+          <t>1693362; 1768036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1661291; 1832165</t>
+          <t>1624019; 1688142</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3470960; 3715138</t>
+          <t>3335002; 3437124</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>482535</t>
+          <t>526705</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>491774</t>
+          <t>545700</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>974309</t>
+          <t>1072404</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>457917; 503817</t>
+          <t>499883; 551625</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472054; 508704</t>
+          <t>525466; 564743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>944379; 999954</t>
+          <t>1038332; 1103637</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2704679</t>
+          <t>2692265</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2822566</t>
+          <t>2843277</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5527245</t>
+          <t>5535542</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2640904; 2813367</t>
+          <t>2642087; 2735554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2729210; 2933743</t>
+          <t>2796093; 2883019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5410152; 5688034</t>
+          <t>5470766; 5594658</t>
         </is>
       </c>
     </row>
